--- a/rsvp_forms/010_media_partner_luncheon_rsvp--rsvp_forms.xlsx
+++ b/rsvp_forms/010_media_partner_luncheon_rsvp--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'options':_[{'label':_'gluten-free'},_{'value':_'gluten-free'},_{'label':_'vegetarian'},_{'value':_'vegetarian'},_{'label':_'vegan'},_{'value':_'vegan'}]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'options': [{'label': 'Gluten-free'}, {'value': 'gluten-free'}, {'label': 'Vegetarian'}, {'value': 'vegetarian'}, {'label': 'Vegan'}, {'value': 'vegan'}]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'no_restrictions',_'value':_'no_restrictions'}</t>
+          <t>no_restrictions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'No Restrictions', 'value': 'no_restrictions'}</t>
+          <t>No Restrictions</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'gluten-free',_'value':_'gluten-free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Gluten-free', 'value': 'gluten-free'}</t>
+          <t>Gluten-free</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian',_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian', 'value': 'vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan', 'value': 'vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'accept',_'value':_'accept'}</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Accept', 'value': 'accept'}</t>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'decline',_'value':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Decline', 'value': 'decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'company_1',_'value':_'company-1'}</t>
+          <t>company_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Company 1', 'value': 'company-1'}</t>
+          <t>Company 1</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'company_2',_'value':_'company-2'}</t>
+          <t>company_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Company 2', 'value': 'company-2'}</t>
+          <t>Company 2</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'ceo',_'value':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'CEO', 'value': 'ceo'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'cfo',_'value':_'cfo'}</t>
+          <t>cfo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'CFO', 'value': 'cfo'}</t>
+          <t>CFO</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'cto',_'value':_'cto'}</t>
+          <t>cto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'CTO', 'value': 'cto'}</t>
+          <t>CTO</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
